--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderTemplate.xlsx
@@ -16,9 +16,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -37,6 +44,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -55,6 +69,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -70,21 +91,13 @@
   </si>
   <si>
     <r>
-      <t>*</t>
-    </r>
-    <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>交货仓库</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>*</t>
     </r>
     <r>
@@ -1077,25 +1090,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="2" width="10.5" customWidth="1"/>
     <col min="3" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="10.375" customWidth="1"/>
     <col min="5" max="5" width="11.25" customWidth="1"/>
-    <col min="6" max="6" width="10.625" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
-    <col min="8" max="8" width="9.625" customWidth="1"/>
-    <col min="9" max="9" width="10.125" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="19" width="10.25" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="9.625" customWidth="1"/>
+    <col min="8" max="8" width="10.125" customWidth="1"/>
+    <col min="9" max="9" width="10.375" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,16 +1126,13 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576 G$1:G$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576 F$1:F$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">

--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderTemplate.xlsx
@@ -795,6 +795,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>

--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
       <rPr>
@@ -66,28 +66,6 @@
   </si>
   <si>
     <t>计划交期</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>收料组织</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1095,24 +1073,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="2" width="10.5" customWidth="1"/>
     <col min="3" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="10.375" customWidth="1"/>
-    <col min="5" max="5" width="11.25" customWidth="1"/>
-    <col min="6" max="6" width="11.5" customWidth="1"/>
-    <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="10.375" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="10.25" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="9.625" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="8" width="10.375" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="10.25" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1128,16 +1105,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576 F$1:F$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576 E$1:E$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
